--- a/data/industry_cache/20261018/industry_observation.xlsx
+++ b/data/industry_cache/20261018/industry_observation.xlsx
@@ -540,19 +540,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2152</v>
+        <v>1.3053</v>
       </c>
       <c r="D2" t="n">
-        <v>42.69</v>
+        <v>79.2</v>
       </c>
       <c r="E2" t="n">
-        <v>58.43</v>
+        <v>79.47</v>
       </c>
       <c r="F2" t="n">
-        <v>57.74</v>
+        <v>47.97</v>
       </c>
       <c r="G2" t="n">
-        <v>96.41</v>
+        <v>86.97</v>
       </c>
       <c r="H2" t="n">
         <v>-50.42</v>
@@ -573,28 +573,28 @@
         <v>-38.42</v>
       </c>
       <c r="N2" t="n">
-        <v>6.46</v>
+        <v>-1.34</v>
       </c>
       <c r="O2" t="n">
-        <v>7.93</v>
+        <v>-10.63</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.22</v>
+        <v>-15.84</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.657</v>
+        <v>4.538</v>
       </c>
       <c r="D3" t="n">
-        <v>30.24</v>
+        <v>23.66</v>
       </c>
       <c r="E3" t="n">
-        <v>89.39</v>
+        <v>57.94</v>
       </c>
       <c r="F3" t="n">
-        <v>44.64</v>
+        <v>38.45</v>
       </c>
       <c r="G3" t="n">
-        <v>70.65000000000001</v>
+        <v>53.67</v>
       </c>
       <c r="H3" t="n">
         <v>11.02</v>
@@ -647,13 +647,13 @@
         <v>19.67</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>-6.31</v>
       </c>
       <c r="O3" t="n">
-        <v>8.91</v>
+        <v>-12.58</v>
       </c>
       <c r="P3" t="n">
-        <v>17.02</v>
+        <v>-2.43</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.591</v>
+        <v>0.6218</v>
       </c>
       <c r="D4" t="n">
-        <v>29.91</v>
+        <v>29.42</v>
       </c>
       <c r="E4" t="n">
-        <v>77.04000000000001</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>20.73</v>
+        <v>19.11</v>
       </c>
       <c r="G4" t="n">
-        <v>41.95</v>
+        <v>37.29</v>
       </c>
       <c r="H4" t="n">
         <v>3.23</v>
@@ -721,13 +721,13 @@
         <v>0.65</v>
       </c>
       <c r="N4" t="n">
-        <v>3.23</v>
+        <v>-1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>1.05</v>
+        <v>-6.75</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.91</v>
+        <v>-12.12</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -739,10 +739,10 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.6791</v>
+        <v>5.1574</v>
       </c>
       <c r="D5" t="n">
-        <v>22.51</v>
+        <v>15.51</v>
       </c>
       <c r="E5" t="n">
-        <v>64.77</v>
+        <v>19.83</v>
       </c>
       <c r="F5" t="n">
-        <v>48.93</v>
+        <v>26.9</v>
       </c>
       <c r="G5" t="n">
-        <v>77.27</v>
+        <v>33.62</v>
       </c>
       <c r="H5" t="n">
         <v>10.68</v>
@@ -795,13 +795,13 @@
         <v>-3.71</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>-5.31</v>
       </c>
       <c r="O5" t="n">
-        <v>11.35</v>
+        <v>-17.22</v>
       </c>
       <c r="P5" t="n">
-        <v>51.35</v>
+        <v>7.72</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -813,10 +813,10 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -836,19 +836,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.8026</v>
+        <v>18.009</v>
       </c>
       <c r="D6" t="n">
-        <v>80.47</v>
+        <v>50.47</v>
       </c>
       <c r="E6" t="n">
-        <v>95.95999999999999</v>
+        <v>61.97</v>
       </c>
       <c r="F6" t="n">
-        <v>55.94</v>
+        <v>47.12</v>
       </c>
       <c r="G6" t="n">
-        <v>82.93000000000001</v>
+        <v>73.63</v>
       </c>
       <c r="H6" t="n">
         <v>6.49</v>
@@ -869,16 +869,16 @@
         <v>0.43</v>
       </c>
       <c r="N6" t="n">
-        <v>0.15</v>
+        <v>-10.09</v>
       </c>
       <c r="O6" t="n">
-        <v>10.24</v>
+        <v>-17.11</v>
       </c>
       <c r="P6" t="n">
-        <v>69.34</v>
+        <v>6.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -910,19 +910,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.5901</v>
+        <v>3.659</v>
       </c>
       <c r="D7" t="n">
-        <v>24.97</v>
+        <v>23.77</v>
       </c>
       <c r="E7" t="n">
-        <v>19.79</v>
+        <v>10.53</v>
       </c>
       <c r="F7" t="n">
-        <v>27.86</v>
+        <v>36.14</v>
       </c>
       <c r="G7" t="n">
-        <v>17.3</v>
+        <v>40.56</v>
       </c>
       <c r="H7" t="n">
         <v>7.54</v>
@@ -943,13 +943,13 @@
         <v>12.45</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>-4.22</v>
       </c>
       <c r="O7" t="n">
-        <v>0.23</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-11.67</v>
+        <v>-27.92</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -961,10 +961,10 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -984,19 +984,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.0936</v>
+        <v>2.2628</v>
       </c>
       <c r="D8" t="n">
-        <v>14.85</v>
+        <v>14.59</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>51.59</v>
       </c>
       <c r="F8" t="n">
-        <v>28.88</v>
+        <v>25.63</v>
       </c>
       <c r="G8" t="n">
-        <v>48.8</v>
+        <v>34.01</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -1011,13 +1011,13 @@
         <v>-0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0.65</v>
+        <v>-0.24</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5</v>
+        <v>-3.94</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.36</v>
+        <v>-7.78</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1052,19 +1052,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.2137</v>
+        <v>3.6178</v>
       </c>
       <c r="D9" t="n">
-        <v>19.98</v>
+        <v>21.12</v>
       </c>
       <c r="E9" t="n">
-        <v>10.61</v>
+        <v>28.81</v>
       </c>
       <c r="F9" t="n">
-        <v>38.84</v>
+        <v>30.46</v>
       </c>
       <c r="G9" t="n">
-        <v>85.65000000000001</v>
+        <v>57.96</v>
       </c>
       <c r="H9" t="n">
         <v>-13.64</v>
@@ -1085,13 +1085,13 @@
         <v>-15.08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.14</v>
+        <v>2.57</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.04</v>
+        <v>0.36</v>
       </c>
       <c r="P9" t="n">
-        <v>-17.26</v>
+        <v>-18.03</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1103,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1126,19 +1126,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.512</v>
+        <v>0.5395</v>
       </c>
       <c r="D10" t="n">
-        <v>24.93</v>
+        <v>24.18</v>
       </c>
       <c r="E10" t="n">
-        <v>67.54000000000001</v>
+        <v>58.09</v>
       </c>
       <c r="F10" t="n">
-        <v>41.31</v>
+        <v>41.3</v>
       </c>
       <c r="G10" t="n">
-        <v>62.76</v>
+        <v>62.32</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         <v>-0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>2.53</v>
+        <v>-1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>5.71</v>
+        <v>-5.69</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.95</v>
+        <v>-10.29</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1171,10 +1171,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7734</v>
+        <v>0.8213</v>
       </c>
       <c r="D11" t="n">
-        <v>32.45</v>
+        <v>32.17</v>
       </c>
       <c r="E11" t="n">
-        <v>88.92</v>
+        <v>85.75</v>
       </c>
       <c r="F11" t="n">
-        <v>33.55</v>
+        <v>39.44</v>
       </c>
       <c r="G11" t="n">
-        <v>46.73</v>
+        <v>56.86</v>
       </c>
       <c r="H11" t="n">
         <v>9.199999999999999</v>
@@ -1227,13 +1227,13 @@
         <v>-1.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>-4.15</v>
       </c>
       <c r="O11" t="n">
-        <v>5.76</v>
+        <v>-7.35</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.7</v>
+        <v>-12.67</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1245,10 +1245,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1268,52 +1268,52 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.3566</v>
+        <v>6.7437</v>
       </c>
       <c r="D12" t="n">
-        <v>33.76</v>
+        <v>31.4</v>
       </c>
       <c r="E12" t="n">
-        <v>69.98999999999999</v>
+        <v>54.92</v>
       </c>
       <c r="F12" t="n">
-        <v>54.75</v>
+        <v>43.03</v>
       </c>
       <c r="G12" t="n">
-        <v>96.48999999999999</v>
+        <v>84.17</v>
       </c>
       <c r="H12" t="n">
-        <v>13.29</v>
+        <v>13.12</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>9.4</v>
+        <v>9.23</v>
       </c>
       <c r="K12" t="n">
-        <v>13.32</v>
+        <v>11.57</v>
       </c>
       <c r="L12" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M12" t="n">
-        <v>6.63</v>
+        <v>4.88</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.43</v>
+        <v>-4.63</v>
       </c>
       <c r="O12" t="n">
-        <v>4.22</v>
+        <v>-3.85</v>
       </c>
       <c r="P12" t="n">
-        <v>-11.45</v>
+        <v>-15.42</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1322,7 +1322,7 @@
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1342,19 +1342,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.4189</v>
+        <v>2.6982</v>
       </c>
       <c r="D13" t="n">
-        <v>20.98</v>
+        <v>21.63</v>
       </c>
       <c r="E13" t="n">
-        <v>54.24</v>
+        <v>57.63</v>
       </c>
       <c r="F13" t="n">
-        <v>28.8</v>
+        <v>27.16</v>
       </c>
       <c r="G13" t="n">
-        <v>48.72</v>
+        <v>43.76</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
@@ -1375,13 +1375,13 @@
         <v>-0.88</v>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>-1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.79</v>
+        <v>-1.73</v>
       </c>
       <c r="P13" t="n">
-        <v>4.06</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1416,19 +1416,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.8702</v>
+        <v>2.0532</v>
       </c>
       <c r="D14" t="n">
-        <v>17.06</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="n">
-        <v>79.81</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>21.02</v>
+        <v>22.02</v>
       </c>
       <c r="G14" t="n">
-        <v>50.64</v>
+        <v>54.99</v>
       </c>
       <c r="H14" t="n">
         <v>16.96</v>
@@ -1449,13 +1449,13 @@
         <v>7.82</v>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>-1.65</v>
       </c>
       <c r="O14" t="n">
-        <v>0.42</v>
+        <v>-3</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.79</v>
+        <v>-7.86</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1467,10 +1467,10 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1490,19 +1490,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8423</v>
+        <v>0.9298</v>
       </c>
       <c r="D15" t="n">
-        <v>20.13</v>
+        <v>13.25</v>
       </c>
       <c r="E15" t="n">
-        <v>66.90000000000001</v>
+        <v>36.48</v>
       </c>
       <c r="F15" t="n">
-        <v>35.1</v>
+        <v>58.68</v>
       </c>
       <c r="G15" t="n">
-        <v>57.89</v>
+        <v>91.42</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1517,28 +1517,28 @@
         <v>-0.33</v>
       </c>
       <c r="N15" t="n">
-        <v>2.59</v>
+        <v>-6.27</v>
       </c>
       <c r="O15" t="n">
-        <v>4.7</v>
+        <v>-2.36</v>
       </c>
       <c r="P15" t="n">
-        <v>-11.88</v>
+        <v>-19.27</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1558,19 +1558,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8192</v>
+        <v>0.8581</v>
       </c>
       <c r="D16" t="n">
-        <v>34.96</v>
+        <v>31.79</v>
       </c>
       <c r="E16" t="n">
-        <v>58.75</v>
+        <v>39.5</v>
       </c>
       <c r="F16" t="n">
-        <v>34.91</v>
+        <v>36.18</v>
       </c>
       <c r="G16" t="n">
-        <v>58.61</v>
+        <v>60.45</v>
       </c>
       <c r="H16" t="n">
         <v>2.06</v>
@@ -1591,13 +1591,13 @@
         <v>-5.24</v>
       </c>
       <c r="N16" t="n">
-        <v>3.41</v>
+        <v>-2.12</v>
       </c>
       <c r="O16" t="n">
-        <v>1.06</v>
+        <v>-10.02</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.46</v>
+        <v>-25.53</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1609,10 +1609,10 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1632,19 +1632,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.4965</v>
+        <v>0.5212</v>
       </c>
       <c r="D17" t="n">
-        <v>40.41</v>
+        <v>39.91</v>
       </c>
       <c r="E17" t="n">
-        <v>21.69</v>
+        <v>20.6</v>
       </c>
       <c r="F17" t="n">
-        <v>36.99</v>
+        <v>35.78</v>
       </c>
       <c r="G17" t="n">
-        <v>28.87</v>
+        <v>26.52</v>
       </c>
       <c r="H17" t="n">
         <v>-2</v>
@@ -1665,13 +1665,13 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>3.32</v>
+        <v>-3.5</v>
       </c>
       <c r="O17" t="n">
-        <v>4.96</v>
+        <v>-9.81</v>
       </c>
       <c r="P17" t="n">
-        <v>-13.84</v>
+        <v>-21</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1683,10 +1683,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1706,19 +1706,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.1334</v>
+        <v>6.0873</v>
       </c>
       <c r="D18" t="n">
-        <v>6.17</v>
+        <v>6.5</v>
       </c>
       <c r="E18" t="n">
-        <v>72.84</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>12.28</v>
+        <v>12.77</v>
       </c>
       <c r="G18" t="n">
-        <v>73.44</v>
+        <v>76.05</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1733,13 +1733,13 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>0.02</v>
+        <v>0.43</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.38</v>
+        <v>2.52</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.55</v>
+        <v>5.14</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1751,10 +1751,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1774,19 +1774,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.011</v>
+        <v>5.242</v>
       </c>
       <c r="D19" t="n">
-        <v>11.58</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>17.92</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>38.2</v>
+        <v>13.57</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1801,13 +1801,13 @@
         <v>2.03</v>
       </c>
       <c r="N19" t="n">
-        <v>3.94</v>
+        <v>0.17</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1</v>
+        <v>-6.41</v>
       </c>
       <c r="P19" t="n">
-        <v>-11.25</v>
+        <v>-14.18</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1842,19 +1842,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2021</v>
+        <v>0.2058</v>
       </c>
       <c r="D20" t="n">
-        <v>93.7</v>
+        <v>73.69</v>
       </c>
       <c r="E20" t="n">
-        <v>93.98</v>
+        <v>89.47</v>
       </c>
       <c r="F20" t="n">
-        <v>55.43</v>
+        <v>52.35</v>
       </c>
       <c r="G20" t="n">
-        <v>90.59</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1869,19 +1869,19 @@
         <v>-3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7</v>
+        <v>-5.7</v>
       </c>
       <c r="O20" t="n">
-        <v>10.74</v>
+        <v>-11.01</v>
       </c>
       <c r="P20" t="n">
-        <v>34.83</v>
+        <v>0.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1910,19 +1910,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.883</v>
+        <v>0.889</v>
       </c>
       <c r="D21" t="n">
-        <v>36.03</v>
+        <v>34.35</v>
       </c>
       <c r="E21" t="n">
-        <v>94.14</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>35.75</v>
+        <v>40.58</v>
       </c>
       <c r="G21" t="n">
-        <v>66.34999999999999</v>
+        <v>71.84</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         <v>1.23</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>-7.19</v>
       </c>
       <c r="O21" t="n">
-        <v>6.86</v>
+        <v>-9.91</v>
       </c>
       <c r="P21" t="n">
-        <v>21.4</v>
+        <v>3.58</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
@@ -1955,10 +1955,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -1978,19 +1978,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.2957</v>
+        <v>1.3789</v>
       </c>
       <c r="D22" t="n">
-        <v>13.42</v>
+        <v>14.2</v>
       </c>
       <c r="E22" t="n">
-        <v>90.42</v>
+        <v>92.56</v>
       </c>
       <c r="F22" t="n">
-        <v>29.6</v>
+        <v>23.75</v>
       </c>
       <c r="G22" t="n">
-        <v>47.77</v>
+        <v>25.98</v>
       </c>
       <c r="H22" t="n">
         <v>1.52</v>
@@ -2011,13 +2011,13 @@
         <v>0.11</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>-2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>-6.39</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.59</v>
+        <v>-10.61</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -2029,10 +2029,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2052,19 +2052,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.4611</v>
+        <v>7.9605</v>
       </c>
       <c r="D23" t="n">
-        <v>31.78</v>
+        <v>25.43</v>
       </c>
       <c r="E23" t="n">
-        <v>49.01</v>
+        <v>25.41</v>
       </c>
       <c r="F23" t="n">
-        <v>39.05</v>
+        <v>39.25</v>
       </c>
       <c r="G23" t="n">
-        <v>52.39</v>
+        <v>53.82</v>
       </c>
       <c r="H23" t="n">
         <v>6.2</v>
@@ -2085,13 +2085,13 @@
         <v>0.02</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.87</v>
+        <v>-6.86</v>
       </c>
       <c r="O23" t="n">
-        <v>0.67</v>
+        <v>-13.07</v>
       </c>
       <c r="P23" t="n">
-        <v>19.13</v>
+        <v>-19.07</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2126,19 +2126,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.1859</v>
+        <v>5.8869</v>
       </c>
       <c r="D24" t="n">
-        <v>43.64</v>
+        <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>93.98</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>39.48</v>
+        <v>35.01</v>
       </c>
       <c r="G24" t="n">
-        <v>54.55</v>
+        <v>46.8</v>
       </c>
       <c r="H24" t="n">
         <v>1.6</v>
@@ -2159,16 +2159,16 @@
         <v>-4.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>-7.84</v>
       </c>
       <c r="O24" t="n">
-        <v>8.4</v>
+        <v>-16.42</v>
       </c>
       <c r="P24" t="n">
-        <v>19.08</v>
+        <v>-9.57</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U24" t="n">
         <v>-1</v>
@@ -2200,19 +2200,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.6109</v>
+        <v>2.7304</v>
       </c>
       <c r="D25" t="n">
-        <v>59.69</v>
+        <v>55.52</v>
       </c>
       <c r="E25" t="n">
-        <v>50.75</v>
+        <v>36.48</v>
       </c>
       <c r="F25" t="n">
-        <v>31.28</v>
+        <v>34.91</v>
       </c>
       <c r="G25" t="n">
-        <v>44.1</v>
+        <v>52.42</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2227,13 +2227,13 @@
         <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>1.72</v>
+        <v>-3.57</v>
       </c>
       <c r="O25" t="n">
-        <v>3.28</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.06</v>
+        <v>-8.74</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2268,19 +2268,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.7258</v>
+        <v>4.7916</v>
       </c>
       <c r="D26" t="n">
-        <v>67.65000000000001</v>
+        <v>56.86</v>
       </c>
       <c r="E26" t="n">
-        <v>63.97</v>
+        <v>40.59</v>
       </c>
       <c r="F26" t="n">
-        <v>39.09</v>
+        <v>34.29</v>
       </c>
       <c r="G26" t="n">
-        <v>33.57</v>
+        <v>23.71</v>
       </c>
       <c r="H26" t="n">
         <v>12.66</v>
@@ -2301,13 +2301,13 @@
         <v>12.94</v>
       </c>
       <c r="N26" t="n">
-        <v>1.38</v>
+        <v>-2.8</v>
       </c>
       <c r="O26" t="n">
-        <v>0.41</v>
+        <v>-8.5</v>
       </c>
       <c r="P26" t="n">
-        <v>-13.6</v>
+        <v>-26.98</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2319,10 +2319,10 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2342,19 +2342,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.6308</v>
+        <v>1.8515</v>
       </c>
       <c r="D27" t="n">
-        <v>34.73</v>
+        <v>34.55</v>
       </c>
       <c r="E27" t="n">
-        <v>44.73</v>
+        <v>43.61</v>
       </c>
       <c r="F27" t="n">
-        <v>35.42</v>
+        <v>59.16</v>
       </c>
       <c r="G27" t="n">
-        <v>29.59</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>3.24</v>
@@ -2375,13 +2375,13 @@
         <v>-0.92</v>
       </c>
       <c r="N27" t="n">
-        <v>0.22</v>
+        <v>3.83</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.94</v>
+        <v>-4.06</v>
       </c>
       <c r="P27" t="n">
-        <v>-14.27</v>
+        <v>-21.34</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2416,19 +2416,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.8119</v>
+        <v>5.2828</v>
       </c>
       <c r="D28" t="n">
-        <v>57.04</v>
+        <v>41.46</v>
       </c>
       <c r="E28" t="n">
-        <v>93.27</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>49.14</v>
+        <v>37.23</v>
       </c>
       <c r="G28" t="n">
-        <v>70.26000000000001</v>
+        <v>49.38</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2443,16 +2443,16 @@
         <v>4.72</v>
       </c>
       <c r="N28" t="n">
-        <v>-3.13</v>
+        <v>-11.63</v>
       </c>
       <c r="O28" t="n">
-        <v>10.13</v>
+        <v>-20.99</v>
       </c>
       <c r="P28" t="n">
-        <v>85.06999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2464,7 +2464,7 @@
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2484,19 +2484,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9446</v>
+        <v>1.0833</v>
       </c>
       <c r="D29" t="n">
-        <v>22.77</v>
+        <v>18.84</v>
       </c>
       <c r="E29" t="n">
-        <v>98.59</v>
+        <v>85.91</v>
       </c>
       <c r="F29" t="n">
-        <v>45.46</v>
+        <v>39.04</v>
       </c>
       <c r="G29" t="n">
-        <v>82.79000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2511,16 +2511,16 @@
         <v>-19.59</v>
       </c>
       <c r="N29" t="n">
-        <v>5.13</v>
+        <v>1.43</v>
       </c>
       <c r="O29" t="n">
-        <v>9.9</v>
+        <v>-1.32</v>
       </c>
       <c r="P29" t="n">
-        <v>31.81</v>
+        <v>24.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U29" t="n">
         <v>-1</v>
@@ -2552,19 +2552,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.1858</v>
+        <v>1.2659</v>
       </c>
       <c r="D30" t="n">
-        <v>21.36</v>
+        <v>16.6</v>
       </c>
       <c r="E30" t="n">
-        <v>94.01000000000001</v>
+        <v>72.77</v>
       </c>
       <c r="F30" t="n">
-        <v>28.39</v>
+        <v>24.63</v>
       </c>
       <c r="G30" t="n">
-        <v>72.31999999999999</v>
+        <v>55.06</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2579,16 +2579,16 @@
         <v>3.12</v>
       </c>
       <c r="N30" t="n">
-        <v>3.23</v>
+        <v>-1.02</v>
       </c>
       <c r="O30" t="n">
-        <v>8.75</v>
+        <v>-5.45</v>
       </c>
       <c r="P30" t="n">
-        <v>25.75</v>
+        <v>22.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U30" t="n">
         <v>-1</v>
@@ -2620,19 +2620,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8045</v>
+        <v>0.8061</v>
       </c>
       <c r="D31" t="n">
-        <v>26.31</v>
+        <v>23.43</v>
       </c>
       <c r="E31" t="n">
-        <v>80.90000000000001</v>
+        <v>67.78</v>
       </c>
       <c r="F31" t="n">
-        <v>30.74</v>
+        <v>27.98</v>
       </c>
       <c r="G31" t="n">
-        <v>51.11</v>
+        <v>45.37</v>
       </c>
       <c r="H31" t="n">
         <v>8.66</v>
@@ -2653,13 +2653,13 @@
         <v>9.49</v>
       </c>
       <c r="N31" t="n">
-        <v>1.98</v>
+        <v>-6.38</v>
       </c>
       <c r="O31" t="n">
-        <v>6.79</v>
+        <v>-10.39</v>
       </c>
       <c r="P31" t="n">
-        <v>2.17</v>
+        <v>-9.34</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2671,10 +2671,10 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -2694,19 +2694,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1823</v>
+        <v>0.2019</v>
       </c>
       <c r="D32" t="n">
-        <v>30.39</v>
+        <v>28.24</v>
       </c>
       <c r="E32" t="n">
-        <v>16.55</v>
+        <v>6.36</v>
       </c>
       <c r="F32" t="n">
-        <v>38.72</v>
+        <v>40.3</v>
       </c>
       <c r="G32" t="n">
-        <v>61.58</v>
+        <v>65.02</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2721,16 +2721,16 @@
         <v>0.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.94</v>
+        <v>-1.12</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.54</v>
+        <v>-2.01</v>
       </c>
       <c r="P32" t="n">
-        <v>-27.31</v>
+        <v>-27.67</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
